--- a/artfynd/A 63625-2023 artfynd.xlsx
+++ b/artfynd/A 63625-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63625-2023 artfynd.xlsx
+++ b/artfynd/A 63625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112495410</v>
+        <v>112495481</v>
       </c>
       <c r="B2" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -766,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar under en törstubbe i sandtallskog.</t>
+          <t>På undersidan av törstubbe tillsammans med smalfotad taggsvamp och silkesporing.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,41 +781,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112495481</v>
+        <v>112495410</v>
       </c>
       <c r="B3" t="n">
-        <v>88745</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -877,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På undersidan av törstubbe tillsammans med smalfotad taggsvamp och silkesporing.</t>
+          <t>Äldre fruktkroppar under en törstubbe i sandtallskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +892,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122660513</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Höksälven, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>455168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6667380</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Under bro</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Per Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63625-2023 artfynd.xlsx
+++ b/artfynd/A 63625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112495410</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122660513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>